--- a/JsonConverter/ExcelFiles/OO_Narration.xlsx
+++ b/JsonConverter/ExcelFiles/OO_Narration.xlsx
@@ -1,13 +1,8 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="7" rupBuild="14420"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <fileVersion appName="xl" lastEdited="5" lowestEdited="7" rupBuild="9302"/>
   <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\0_NRUnityProjects\ComputerBasics_DaniTech_Work\JsonConverter\ExcelFiles\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
   <bookViews>
     <workbookView xWindow="12770" yWindow="2240" windowWidth="19820" windowHeight="18420"/>
   </bookViews>
@@ -17,14 +12,14 @@
   <calcPr calcId="0"/>
   <extLst>
     <ext uri="GoogleSheetsCustomDataVersion2">
-      <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" r:id="rId5" roundtripDataChecksum="zgynNiv2YVTupuAxVwKvj3LXvSi69gCaqo2XUeu/LZo="/>
+      <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" r:id="" roundtripDataChecksum="zgynNiv2YVTupuAxVwKvj3LXvSi69gCaqo2XUeu/LZo="/>
     </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="32" uniqueCount="29">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="26" uniqueCount="22">
   <si>
     <t>캐릭터 고유 ID</t>
   </si>
@@ -41,49 +36,11 @@
     <t>Id</t>
   </si>
   <si>
-    <t>Name</t>
-  </si>
-  <si>
-    <t>Description</t>
-  </si>
-  <si>
-    <t>character_hellena_01</t>
+    <t>프롤로그1_줄거리1</t>
     <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
-    <t>헬레나</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>모든 마법을 사용할 수 있는 캐릭터</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>character_victor_01</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>빅토르</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>소환 마법을 사용할 수 있는 캐릭터</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>character_daniel_01</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>다니엘</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>잉여로운 버프 캐릭터</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>스킬</t>
+    <t>narration_prologue_01</t>
     <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
@@ -91,55 +48,4920 @@
     <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
-    <t>SkillList</t>
+    <t>Title</t>
     <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
-    <t>skill_rest_coffee_01</t>
+    <t>PartNumber</t>
     <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
-    <t>skill_fireball_01,skill_normalSword_01</t>
+    <t>NarrationTexts</t>
     <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
-    <t>skill_normalSword_01</t>
+    <t>BackgroundImagePath</t>
     <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
-    <t>캐릭터 별로 무기가 고정인 경우용</t>
+    <t>Images/Prologue/Prologue1CutScene1</t>
     <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
-    <t>UseWeaponId</t>
+    <t>narration_prologue_03</t>
     <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
-    <t>Weapon_Sword_1</t>
+    <t>프롤로그1_줄거리2</t>
     <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
-    <t>Weapon_CoffeeCup_1</t>
+    <t>프롤로그1_줄거리3</t>
     <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
-    <t>Weapon_Braclet_1</t>
+    <r>
+      <t>"</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>그러나</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>호사다마라</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>하였던가</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">. </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>꽃이</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>온</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>세상에</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>흐드러지게</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>피어나던</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>그</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>눈부신</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>나이에</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>장금에게</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>홀연히</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>이름</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>모를</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>몹쓸</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>병이</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>찾아와</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>붉은</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>꽃잎</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>떨어지듯</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>허망하게</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>저물고</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>말았다네</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">. </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>장영심은</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>숨조차</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>쉬기</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>힘든</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>기계의</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>거친</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>굉음</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>속에서</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>매일</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>밤</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>꺼져가는</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>불씨처럼</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>딸의</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>이름만</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>부르며</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>피눈물을</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>흘렸더랬다</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">. </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>차디찬</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>연구실에</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>홀로</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>남은</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>그의</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>가슴속에는</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>오직</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>하나</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>, ‘</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>내</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>딸을</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>그저</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>단</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>한</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>번만이라도</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>다시</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>품에</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>안을</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>수만</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>있다면</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">…’ </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>하는</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>간절하고도</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>애달픈</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>염원만이</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>시린</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>새벽달처럼</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>남아</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>흐르고</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>있었다</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>."</t>
+    </r>
     <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
-    <t>BasicCostumeId</t>
+    <r>
+      <t>"</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>그리하여</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>장영심은</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>자신의</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>모든</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>영혼과</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>평생을</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>바친</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>기술을</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>쏟아부어</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>마치</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>살아</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>숨</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>쉬듯</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>정교하게</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>움직이는</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>목각</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>인형을</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>깎아내기</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>시작했다네</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">. </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>인형의</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>얼굴에는</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>조그만</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>화면이</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>신비롭게</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>박혀</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>있어</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>장금이</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>생전에</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>좋아하던</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>요리와</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>서툰</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>감정들을</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>그림과</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>글자로</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>띄울</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>수</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>있는</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>세상에</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>단</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>하나뿐인</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>기적의</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>발명품이었지</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">.
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>매일</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>밤</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>째깍거리는</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>태엽을</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>감으며</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>장영심은</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>주름진</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>메마른</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>두</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>손을</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>모아</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>하늘에</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>간절히</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>빌고</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>또</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>빌었다네</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>. ‘</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>제발</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">… </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>이</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>정교한</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>나무껍데기에</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>내</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>가여운</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>아이의</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>영혼을</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>잠시만이라도</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>단</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>한</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>순간만이라도</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>불어넣어</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>주소서</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">…’ </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>하고</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>말이네</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>."</t>
+    </r>
     <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
-    <t>Costume_03</t>
+    <t>Images/Prologue/Prologue1CutScene2</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>Images/Prologue/Prologue1CutScene3</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>"</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>아득한</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>옛날</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>당시의</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>조선은</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>땅</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>위로</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>뜨거운</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>증기가</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>뿜어져</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>나오고</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>거대한</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>쇠기어들이</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>맞물려</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>돌아가는</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>세상에서</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>가장</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>눈부시고</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>첨단인</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>격동의</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>나라였다네</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">. </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>이</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>거대한</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>영광의</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>한가운데에는</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>조선의</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>스팀펑크</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>시대를</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>당당히</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>열어젖힌</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>천재</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>과학자</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>장영심이</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>살고</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>있었지</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">. </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>그의</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>특출난</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>재주는</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>당대의</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>임금인</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>연산군자의</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>총애를</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>한</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>몸에</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>받기에</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>부족함이</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>없었으나</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>하늘은</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>그에게</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>천재성을</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>준</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>대신</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>가혹한</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>외로움도</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>함께</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>내렸다네</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">.
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>사랑하는</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>아내를</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>일찍</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>여읜</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>그는</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>홀로</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>남은</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>외딸</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>장장금을</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>눈에</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>넣어도</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>아프지</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>않을</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>귀한</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>자식으로</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>정성껏</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>키워냈다네</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">. </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>아버지를</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>닮아</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>영리했던</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>장금은</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>영혼을</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>울리는</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>요리</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>솜씨로</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>궁중</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>최고의</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>요리사가</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>되어</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>임금의</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>귀여움을</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>독차지했지</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">. </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>마음씨</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>곱고</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>효심</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>깊은</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>장금은</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>매일</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>밤</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>붉은</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>불빛이</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>새어</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>나오는</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>기계실에서</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>어머니의</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>빈자리를</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>깊고</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>따뜻한</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>손맛으로</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>채우며</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>홀로</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>외로이</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>연구하는</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>아버지의</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>유일한</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>등불이</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>되어주었다네</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>."</t>
+    </r>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>narration_prologue_02</t>
     <phoneticPr fontId="5" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="9">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <fonts count="10">
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
@@ -200,6 +5022,13 @@
       <family val="3"/>
       <charset val="129"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="돋움"/>
+      <family val="3"/>
+      <charset val="129"/>
     </font>
   </fonts>
   <fills count="8">
@@ -288,7 +5117,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="17">
+  <cellXfs count="20">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -317,6 +5146,13 @@
     <xf numFmtId="0" fontId="8" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -541,9 +5377,9 @@
   <cols>
     <col min="1" max="1" width="19.453125" style="3" customWidth="1"/>
     <col min="2" max="2" width="19.54296875" style="3" customWidth="1"/>
-    <col min="3" max="3" width="50.7265625" style="3" customWidth="1"/>
-    <col min="4" max="4" width="20.26953125" style="3" customWidth="1"/>
-    <col min="5" max="5" width="30.54296875" style="3" customWidth="1"/>
+    <col min="3" max="3" width="11.08984375" style="3" customWidth="1"/>
+    <col min="4" max="4" width="51.81640625" style="3" customWidth="1"/>
+    <col min="5" max="5" width="47.7265625" style="3" customWidth="1"/>
     <col min="6" max="6" width="26.54296875" style="3" customWidth="1"/>
     <col min="7" max="16384" width="12.54296875" style="3"/>
   </cols>
@@ -556,31 +5392,30 @@
       <c r="C1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="D1" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="E1" s="2" t="s">
-        <v>22</v>
-      </c>
+      <c r="D1" s="2"/>
+      <c r="E1" s="2"/>
     </row>
     <row r="2" spans="1:15" ht="13">
       <c r="A2" s="1" t="s">
         <v>2</v>
       </c>
       <c r="B2" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D2" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="C2" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D2" s="1" t="s">
-        <v>17</v>
-      </c>
       <c r="E2" s="1" t="s">
-        <v>17</v>
+        <v>7</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>17</v>
+        <v>7</v>
+      </c>
+      <c r="G2" s="18" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="3" spans="1:15" s="13" customFormat="1" ht="15.75" customHeight="1">
@@ -588,40 +5423,37 @@
         <v>4</v>
       </c>
       <c r="B3" s="12" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="C3" s="12" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="D3" s="14" t="s">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="E3" s="14" t="s">
-        <v>23</v>
+        <v>11</v>
       </c>
-      <c r="F3" s="15" t="s">
-        <v>27</v>
-      </c>
+      <c r="F3" s="15"/>
+      <c r="G3" s="14"/>
     </row>
     <row r="4" spans="1:15" ht="15.75" customHeight="1">
       <c r="A4" s="4" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
-      <c r="C4" s="4" t="s">
-        <v>9</v>
+      <c r="C4" s="17">
+        <v>1</v>
       </c>
-      <c r="D4" s="5" t="s">
+      <c r="D4" s="19" t="s">
         <v>20</v>
       </c>
       <c r="E4" s="5" t="s">
-        <v>26</v>
+        <v>12</v>
       </c>
-      <c r="F4" s="16" t="s">
-        <v>28</v>
-      </c>
+      <c r="F4" s="16"/>
       <c r="G4" s="5"/>
       <c r="H4" s="5"/>
       <c r="I4" s="5"/>
@@ -634,19 +5466,19 @@
     </row>
     <row r="5" spans="1:15" ht="15.75" customHeight="1">
       <c r="A5" s="4" t="s">
-        <v>10</v>
+        <v>21</v>
       </c>
       <c r="B5" s="6" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
-      <c r="C5" s="6" t="s">
-        <v>12</v>
+      <c r="C5" s="6">
+        <v>2</v>
       </c>
       <c r="D5" s="5" t="s">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="E5" s="5" t="s">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="F5" s="5"/>
       <c r="G5" s="5"/>
@@ -664,16 +5496,16 @@
         <v>13</v>
       </c>
       <c r="B6" s="6" t="s">
-        <v>14</v>
-      </c>
-      <c r="C6" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="D6" s="5" t="s">
-        <v>19</v>
+      <c r="C6" s="6">
+        <v>3</v>
+      </c>
+      <c r="D6" s="19" t="s">
+        <v>17</v>
       </c>
       <c r="E6" s="5" t="s">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="F6" s="5"/>
       <c r="G6" s="5"/>

--- a/JsonConverter/ExcelFiles/OO_Narration.xlsx
+++ b/JsonConverter/ExcelFiles/OO_Narration.xlsx
@@ -1,97 +1,8169 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="12770" yWindow="2240" windowWidth="19820" windowHeight="18420" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView xWindow="12770" yWindow="2240" windowWidth="19820" windowHeight="18420"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="DNTable_Narration" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="DNTable_Narration" sheetId="1" r:id="rId1"/>
   </sheets>
-  <definedNames/>
-  <calcPr calcId="0" fullCalcOnLoad="1"/>
+  <calcPr calcId="0"/>
 </workbook>
 </file>
 
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="60" uniqueCount="53">
+  <si>
+    <t>나레이션 ID</t>
+  </si>
+  <si>
+    <t>나레이션 제목</t>
+  </si>
+  <si>
+    <t>파트 번호</t>
+  </si>
+  <si>
+    <t>나레이션 본문</t>
+  </si>
+  <si>
+    <t>배경 이미지 경로</t>
+  </si>
+  <si>
+    <t>배경 이미지 경로 목록(| 구분)</t>
+  </si>
+  <si>
+    <t>BGM 경로</t>
+  </si>
+  <si>
+    <t>다음 그룹 이름</t>
+  </si>
+  <si>
+    <t>string</t>
+  </si>
+  <si>
+    <t>int</t>
+  </si>
+  <si>
+    <t>Id</t>
+  </si>
+  <si>
+    <t>Title</t>
+  </si>
+  <si>
+    <t>PartNumber</t>
+  </si>
+  <si>
+    <t>NarrationTexts</t>
+  </si>
+  <si>
+    <t>BackgroundImagePath</t>
+  </si>
+  <si>
+    <t>BackgroundImagePaths</t>
+  </si>
+  <si>
+    <t>BGMPath</t>
+  </si>
+  <si>
+    <t>NextGroup</t>
+  </si>
+  <si>
+    <t>narration_prologue_01</t>
+  </si>
+  <si>
+    <t>프롤로그1_줄거리1</t>
+  </si>
+  <si>
+    <t>Images/BackGround/Prologue1CutScene1</t>
+  </si>
+  <si>
+    <t>narration_prologue_02</t>
+  </si>
+  <si>
+    <t>프롤로그1_줄거리2</t>
+  </si>
+  <si>
+    <t>"그러나 호사다마라 하였던가. 꽃이 온 세상에 흐드러지게 피어날듯 그 눈부신 나이에, 장금에게 홀연히 이름 모를 몹쓸 병이 찾아와 붉은 꽃잎 떨어지듯 허망하게 저물고 말았다네. 장영심은 숨조차 쉬기 힘든 기계의 거친 굉음 속에서, 매일 밤 꺼져가는 불씨처럼 딸의 이름만 부르며 피눈물을 흘렸더랬다. 차디찬 연구실에 홀로 남은 그의 가슴속에는 오직 하나, ‘내 딸을, 그저 단 한 번만이라도 다시 품에 안을 수만 있다면…’ 하는 간절하고도 애달픈 염원만이 시린 새벽달처럼 남아 흐르고 있었다네."</t>
+  </si>
+  <si>
+    <t>Images/BackGround//Prologue1CutScene2</t>
+  </si>
+  <si>
+    <t>narration_prologue_03</t>
+  </si>
+  <si>
+    <t>프롤로그1_줄거리3</t>
+  </si>
+  <si>
+    <t>"그리하여 장영심은 자신의 모든 영혼과 평생을 바친 기술을 쏟아부어, 마치 살아 숨 쉬듯 정교하게 움직이는 목각 인형을 깎아내기 시작했다네. 인형의 얼굴에는 조그만 화면이 신비롭게 박혀 있어, 장금이 생전에 좋아하던 요리와 서툰 감정들을 그림과 글자로 띄울 수 있는 세상에 단 하나뿐인 기적의 발명품이었지."
+매일 밤 째깍거리는 태엽을 감으며, 장영심은 주름진 메마른 두 손을 모아 하늘에 간절히 빌고 또 빌었다네. ‘제발… 이 정교한 나무껍데기에, 내 가여운 아이의 영혼을 잠시만이라도, 단 한 순간만이라도 불어넣어 주소서…’ 하고 말이네."</t>
+  </si>
+  <si>
+    <t>Images/Background/Prologue1CutScene3</t>
+  </si>
+  <si>
+    <t>narration_prologue_04</t>
+  </si>
+  <si>
+    <t>프롤로그2_줄거리4</t>
+  </si>
+  <si>
+    <t>"장영심은 잃어버린 딸 장금이가 생전 가장 아끼던 꽃의 이름을 따, 그 목각 인형에게 ‘모란’이라는 어여쁜 이름을 지어주었다네. 모란은 아버지의 따스한 손길 아래 아장거리는 걸음마부터 다정한 말씨, 그리고 마음을 담아 밥을 짓는 법까지 하나하나 세상을 배워나갔지. 신기하게도 모란은 옛 장금이처럼 요리에 천재적인 재능을 보이며 점차 딸의 모습을 쏙 빼닮아갔어. 비록 투박한 나무 몸뚱이였으나, 두 사람이 붉은 화덕 앞에서 함께 요리하며 웃음 짓던 그 공방은 세상 어느 곳보다 따뜻한 행복으로 가득 차 있었다네."</t>
+  </si>
+  <si>
+    <t>Images/Background/Prologue2CutScene1</t>
+  </si>
+  <si>
+    <t>narration_prologue_05</t>
+  </si>
+  <si>
+    <t>프롤로그2_줄거리5</t>
+  </si>
+  <si>
+    <t>"아침마다 들려오는 모란의 사랑스러운 목소리에 장영심은 시린 가슴을 녹이며 깊은 행복을 느꼈다네. 허나 영원할 것 같았던 그 온기도 무심한 세월 앞에서는 속절없이 스러지고 말았지. 기계 장치들은 녹슬어갔고, 그의 육신 또한 쇠약해져 죽음의 문턱에 다다랐다네. 숨을 거두기 직전, 장영심은 모란의 나뭇결 손을 꼭 쥐고 떨리는 목소리로 마지막 당부를 남겼어.
+“모란아… 이 차가운 기계 몸으로 세상에 태어난 이유를 부디 잊지 말거라. 세상의 그늘진 곳, 도움이 필요한 가여운 자들을 위해 살아가렴. 네가 지어 올린 따뜻한 밥 한 끼가 사람들의 꽁꽁 언 마음을 녹일 수만 있다면… 그것이야말로 네가 세상에 숨 쉬고 있다는 가장 눈부신 증거란다.”
+모란이 눈물 대신 얼굴 화면에 슬픈 파형을 일렁이며 고개를 끄덕이자, 장영심은 남은 힘을 다해 자신의 낡은 갓을 씌워주고 딸 장금이가 입던 요리사복을 품에 안겨준 뒤 조용히 눈을 감았다네. 그렇게 홀로 남은 모란의 주위로 차가운 적막만이 내려앉았지."</t>
+  </si>
+  <si>
+    <t>Images/Background/Prologue2CutScene2</t>
+  </si>
+  <si>
+    <t>narration_prologue_06</t>
+  </si>
+  <si>
+    <t>프롤로그2_줄거리6</t>
+  </si>
+  <si>
+    <t>Images/Background/Prologue2CutScene3</t>
+  </si>
+  <si>
+    <t>narration_prologue_07</t>
+  </si>
+  <si>
+    <t>시나리오1_줄거리1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">“모란이 지어내는 요리는 결코 평범한 음식이 아니었다네. 장장금의 따뜻한 영혼이 한데 어우러져 빚어낸, 세상에 단 하나뿐인 영묘한 기적의 음식이었지.
+먹는 이의 가장 깊고 간절한 갈망을 헤아려, 그 소원을 풀어주고, 차갑게 얼어붙은 마음을 선한 쪽으로 되돌려주는 마법 같은 치유의 힘이 깃들어 있었다네.
+그 날 배고픔에 지친 작은 강아지 하나가 모란의 집에 스며들어 이 장영심의 제삿상을 허겁지겁 먹어 치우니, 재익의 몸 속에서 뜨거운 기운이 용솟음치며, 털이 곤두서고, 몸이 부풀며, 네 다리가 두 다리로 변하는 기이한 변화가 일어났다네.
+그의 오랜 세월 마음속 깊이 간직했던, ‘사람이 되어 춘양 아씨를 모시고 싶다’라는 그 간절한 소원이 모란의 음식으로 인해 마침내 이루어진 것이었네.”
+</t>
+  </si>
+  <si>
+    <t>narration_prologue_08</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>프리파이널_줄거리8</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>Images/Background/Prologue2CutScene3</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>"</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>아득한</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>옛날</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>당시의</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>조선은</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>땅</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>위로</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>뜨거운</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>증기가</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>뿜어져</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>나오고</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>거대한</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>쇠기어들이</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>맞물려</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>돌아가는</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>세상에서</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>가장</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>눈부시고</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>첨단인</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>격동의</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>나라였다네</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">. </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>이</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>거대한</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>영광의</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>한가운데에는</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>조선의</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>스팀펑크</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>시대를</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>당당히</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>열어젖힌</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>천재</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>과학자</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>장영심이</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>살고</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>있었지</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">. </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>그의</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>특출난</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>재주는</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>당대의</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>임금인</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>연산군자의</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>총애를</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>한</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>몸에</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>받기에</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>부족함이</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>없었으나</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>하늘은</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>그에게</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>천재성을</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>준</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>대신</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>가혹한</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>외로움도</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>함께</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>내렸다네</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">."
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>사랑하는</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>아내를</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>일찍</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>여읜</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>그는</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>홀로</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>남은</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>외딸</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>장장금을</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>눈에</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>넣어도</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>아프지</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>않을</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>귀한</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>자식으로</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>정성껏</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>키워냈다네</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">. </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>아버지를</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>닮아</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>영리했던</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>장금은</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>영혼을</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>울리는</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>요리</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>솜씨로</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>궁중</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>최고의</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>요리사가</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>되어</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>임금의</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>귀여움을</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>독차지했지</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">. </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>마음씨</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>곱고</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>효심</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>깊은</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>장금은</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>매일</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>밤</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>붉은</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>불빛이</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>새어</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>나오는</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>기계실에서</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>어머니의</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>빈자리를</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>깊고</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>따뜻한</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>손맛으로</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>채우며</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>홀로</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>외로이</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>연구하는</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>아버지의</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>유일한</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>등불이</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>되어주었다네</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>."</t>
+    </r>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>"</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>그</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>무렵</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>찬란했던</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>조선은</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>칠흑</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>같은</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>어둠</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>속으로</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>속절없이</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>가라앉고</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>있었다네</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">. </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>조선의</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>놀라운</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>기술을</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>탐낸</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>외세의</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>위협이</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>끊이지</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>않자</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>임금</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>연산군은</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>극심한</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>번뇌</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>속에서</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>마음에</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>깊은</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>병을</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>얻고</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>말았지</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">. </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>설상가상으로</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>입맛을</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>달래주던</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>으뜸</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>요리사</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>장금과</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>기적을</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>빚어내던</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>천재</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>과학자</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>장영심마저</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>연이어</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>세상을</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>떠나버리니</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>임금의</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>광기를</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>잠재울</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>방도도</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>조선의</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>톱니바퀴도</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>모두</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>멈춰버린</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>게야</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">.
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>이성을</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>잃고</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>괴팍해진</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>임금은</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>분노와</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>우울에</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>휩싸여</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>탐관오리들을</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>풀었고</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>백성들의</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>삶은</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>가혹하게</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>짓밟히고</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>말았다네</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">. </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>온</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>나라에</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>굶주림과</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>곡소리가</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>하늘을</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>찌르던</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>바로</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>그</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>비통한</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>때</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">…… </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>굶주린</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>백성을</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>구하고</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>병든</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>조선의</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>마음을</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>치유하기</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>위한</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>모란의</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>위대한</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>여정이</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>마침내</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>첫발을</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>내딛게</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>된</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>것이라네</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">."
+</t>
+    </r>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>“</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>천재</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>과학자</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>장영심과</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>으뜸</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>요리사</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>장금이</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>떠나간</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>뒤</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>분노와</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>우울이라는</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>차가운</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>쇠사슬에</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>묶인</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>임금</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>연산군자의</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>광기는</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>마침내</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>극에</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>달했다네</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">. </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>조정의</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>신하들은</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>왕의</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>명령을</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>거부했고</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>멈춰버린</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>조선의</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>톱니바퀴처럼</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>국가는</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>통제력을</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>잃고</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>삐걱거렸지</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">.
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>사방에</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>적을</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>둔</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>임금은</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>누군가</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>역모를</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>꾸미고</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>있다는</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>극심한</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>피해망상에</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>사로잡혔고</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>마침내</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>팔도를</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>누비며</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>굶주린</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>민심을</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>위로한다는</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>모란</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>일당의</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>소문을</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>듣게</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>되네</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">. </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>왕은</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>그들을</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>백성의</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>영웅이</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>아닌</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>민심을</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>어지럽혀</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>왕권을</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>위협하는</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> ‘</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>음식</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>도적</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>’</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>이자</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>역당의</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>무리로</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>규정하고</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>싹</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>다</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>잡아들이라</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>명한</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>게야</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">.
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>서슬</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>퍼런</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>칼날이</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>번뜩이는</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>대전으로</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>끌려온</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>모란</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>일행에게</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>내려진</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>엄포는</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>단</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>하나</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">! </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>임금의</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>메마른</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>입맛을</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>만족시키지</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>못한다면</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>그</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>요상한</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>나무목과</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>해괴하게</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>생긴</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>개</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>목은</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>물론이고</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>가녀린</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>춘양의</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>목마저</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>광화문</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>거리에</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>매달겠다는</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>참혹한</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>엄포를</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>놓은</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>절체절명의</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>위기였지</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">.
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>이</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>칠흑</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>같은</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>어둠</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>속에서</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>아버지가</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>남긴</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>숭고한</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>유언과</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>도탄에</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>빠진</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>백성들을</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>구하기</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>위해</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>모란은</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>차가운</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>강철</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>심장을</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>움켜쥐고</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>목숨을</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>건</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>마지막</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>요리의</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>불씨를</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>지피기</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>시작한</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>게야</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>.”</t>
+    </r>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>narration_Epilogue_01</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>에필로그_줄거리1</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>Images/Background/</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>“</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>그</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>후로도</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>오랫동안</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>모란의</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>요리마차는</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>하얀</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>김을</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>흩날리며</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>조선</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>팔도의</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>굽이진</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>길을</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>누볐다네</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">. </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>슬픔과</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>굶주림이</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>고인</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>곳이라면</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>어디든</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>찾아가</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>위로의</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>한</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>그릇을</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>건네니</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>모란은</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>강철</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>심장</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>속에</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>아버지의</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>숭고한</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>유언을</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>새겼고</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>재익은</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>굶주린</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>이들의</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>벗이</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>되었으며</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>춘양은</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>그</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>길을</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>비추는</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>따스한</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>봄바람이</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>되었구나</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">.
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>조정의</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>이몽룡은</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>흩어진</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>민심을</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>달래고</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>연산군자</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>왕은</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>뛰어난</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>기술자들을</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>다시</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>불러</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>국력을</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>일으키니</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>백성들의</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>웃음소리가</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>마침내</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>강산에</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>가득해졌도다</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">.
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>그들의</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>마차는</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>머나먼</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>훗날까지도</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>여전히</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>누군가의</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>멍든</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>마음을</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>치유하기</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>위해</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>쉼</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>없이</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>달리고</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>있다네</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>.”</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t/>
+    </r>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+</sst>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
-  <fonts count="11">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <fonts count="8">
     <font>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
       <name val="Arial"/>
-      <color rgb="FF000000"/>
-      <sz val="10"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
       <name val="&quot;맑은 고딕&quot;"/>
+      <family val="3"/>
       <charset val="129"/>
-      <family val="3"/>
-      <color rgb="FF000000"/>
-      <sz val="10"/>
     </font>
     <font>
+      <sz val="10"/>
+      <color theme="1"/>
       <name val="Arial"/>
       <family val="2"/>
-      <color theme="1"/>
-      <sz val="10"/>
     </font>
     <font>
-      <name val="&quot;맑은 고딕&quot;"/>
-      <charset val="129"/>
-      <family val="3"/>
-      <color rgb="FF008000"/>
-      <sz val="11"/>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="Arial"/>
+      <family val="2"/>
     </font>
     <font>
+      <sz val="8"/>
       <name val="Arial"/>
-      <family val="2"/>
-      <color rgb="FF000000"/>
-      <sz val="10"/>
-    </font>
-    <font>
-      <name val="Arial"/>
+      <family val="3"/>
       <charset val="129"/>
-      <family val="3"/>
-      <sz val="8"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
       <name val="Arial"/>
       <family val="2"/>
-      <color rgb="FF000000"/>
-      <sz val="10"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <name val="맑은 고딕"/>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="돋움"/>
+      <family val="3"/>
       <charset val="129"/>
-      <family val="3"/>
-      <color rgb="FF000000"/>
-      <sz val="10"/>
     </font>
     <font>
+      <b/>
+      <sz val="10"/>
       <name val="Arial"/>
-      <charset val="129"/>
-      <family val="3"/>
-      <color rgb="FF000000"/>
-      <sz val="10"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="돋움"/>
-      <charset val="129"/>
-      <family val="3"/>
-      <color rgb="FF000000"/>
-      <sz val="10"/>
-    </font>
-    <font>
-      <b val="1"/>
+      <family val="2"/>
     </font>
   </fonts>
-  <fills count="11">
+  <fills count="10">
     <fill>
-      <patternFill/>
+      <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
@@ -122,29 +8194,23 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.7999816888943144"/>
-        <bgColor rgb="FFC6EFCE"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.7999816888943144"/>
+        <fgColor theme="7" tint="0.79998168889431442"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00D9EAF7"/>
+        <fgColor rgb="FFD9EAF7"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FCE4D6"/>
+        <fgColor rgb="FFFCE4D6"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00E2F0D9"/>
+        <fgColor rgb="FFE2F0D9"/>
       </patternFill>
     </fill>
   </fills>
@@ -190,137 +8256,68 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="27">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+  <cellXfs count="22">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="6" fillId="7" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="8" fillId="7" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="7" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="8" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="7" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="1" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="5" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="7" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="10" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="7" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="표준" xfId="0" builtinId="0"/>
   </cellStyles>
+  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
-  <colors>
-    <indexedColors>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008000"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00808000"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="00C0C0C0"/>
-      <rgbColor rgb="00808080"/>
-      <rgbColor rgb="009999FF"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00FFFFCC"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00660066"/>
-      <rgbColor rgb="00FF8080"/>
-      <rgbColor rgb="000066CC"/>
-      <rgbColor rgb="00CCCCFF"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="0000CCFF"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00CCFFCC"/>
-      <rgbColor rgb="00FFFF99"/>
-      <rgbColor rgb="0099CCFF"/>
-      <rgbColor rgb="00FF99CC"/>
-      <rgbColor rgb="00CC99FF"/>
-      <rgbColor rgb="00FFCC99"/>
-      <rgbColor rgb="003366FF"/>
-      <rgbColor rgb="0033CCCC"/>
-      <rgbColor rgb="0099CC00"/>
-      <rgbColor rgb="00FFCC00"/>
-      <rgbColor rgb="00FF9900"/>
-      <rgbColor rgb="00FF6600"/>
-      <rgbColor rgb="00666699"/>
-      <rgbColor rgb="00969696"/>
-      <rgbColor rgb="00003366"/>
-      <rgbColor rgb="00339966"/>
-      <rgbColor rgb="00003300"/>
-      <rgbColor rgb="00333300"/>
-      <rgbColor rgb="00993300"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00333399"/>
-      <rgbColor rgb="00333333"/>
-    </indexedColors>
-  </colors>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
@@ -521,605 +8518,512 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
-    <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O35"/>
-  <sheetFormatPr baseColWidth="8" defaultColWidth="12.54296875" defaultRowHeight="15" customHeight="1"/>
+  <dimension ref="A1:O1000"/>
+  <sheetFormatPr defaultColWidth="14" defaultRowHeight="15" customHeight="1"/>
   <cols>
-    <col width="14" customWidth="1" style="3" min="1" max="1"/>
-    <col width="14" customWidth="1" style="3" min="2" max="2"/>
-    <col width="14" customWidth="1" style="3" min="3" max="3"/>
-    <col width="14" customWidth="1" style="3" min="4" max="4"/>
-    <col width="15" customWidth="1" style="3" min="5" max="5"/>
-    <col width="24" customWidth="1" style="3" min="6" max="6"/>
-    <col width="14" customWidth="1" style="3" min="7" max="16384"/>
-    <col width="14" customWidth="1" min="8" max="8"/>
+    <col min="1" max="4" width="14" style="2" customWidth="1"/>
+    <col min="5" max="5" width="15" style="2" customWidth="1"/>
+    <col min="6" max="6" width="24" style="2" customWidth="1"/>
+    <col min="7" max="7" width="14" style="2" customWidth="1"/>
+    <col min="8" max="8" width="14" customWidth="1"/>
+    <col min="9" max="16384" width="14" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" ht="15.75" customHeight="1">
-      <c r="A1" s="20" t="inlineStr">
-        <is>
-          <t>나레이션 ID</t>
-        </is>
+    <row r="1" spans="1:15" ht="15.75" customHeight="1">
+      <c r="A1" s="15" t="s">
+        <v>0</v>
       </c>
-      <c r="B1" s="20" t="inlineStr">
-        <is>
-          <t>나레이션 제목</t>
-        </is>
+      <c r="B1" s="15" t="s">
+        <v>1</v>
       </c>
-      <c r="C1" s="20" t="inlineStr">
-        <is>
-          <t>파트 번호</t>
-        </is>
+      <c r="C1" s="15" t="s">
+        <v>2</v>
       </c>
-      <c r="D1" s="20" t="inlineStr">
-        <is>
-          <t>나레이션 본문</t>
-        </is>
+      <c r="D1" s="15" t="s">
+        <v>3</v>
       </c>
-      <c r="E1" s="20" t="inlineStr">
-        <is>
-          <t>배경 이미지 경로</t>
-        </is>
+      <c r="E1" s="15" t="s">
+        <v>4</v>
       </c>
-      <c r="F1" s="21" t="inlineStr">
-        <is>
-          <t>배경 이미지 경로 목록(| 구분)</t>
-        </is>
+      <c r="F1" s="16" t="s">
+        <v>5</v>
       </c>
-      <c r="G1" s="21" t="inlineStr">
-        <is>
-          <t>BGM 경로</t>
-        </is>
+      <c r="G1" s="16" t="s">
+        <v>6</v>
       </c>
-      <c r="H1" s="21" t="inlineStr">
-        <is>
-          <t>다음 그룹 이름</t>
-        </is>
+      <c r="H1" s="16" t="s">
+        <v>7</v>
       </c>
     </row>
-    <row r="2" ht="13" customHeight="1">
-      <c r="A2" s="22" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
+    <row r="2" spans="1:15" ht="13" customHeight="1">
+      <c r="A2" s="17" t="s">
+        <v>8</v>
       </c>
-      <c r="B2" s="22" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
+      <c r="B2" s="17" t="s">
+        <v>8</v>
       </c>
-      <c r="C2" s="22" t="inlineStr">
-        <is>
-          <t>int</t>
-        </is>
+      <c r="C2" s="17" t="s">
+        <v>9</v>
       </c>
-      <c r="D2" s="22" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
+      <c r="D2" s="17" t="s">
+        <v>8</v>
       </c>
-      <c r="E2" s="22" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
+      <c r="E2" s="17" t="s">
+        <v>8</v>
       </c>
-      <c r="F2" s="22" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
+      <c r="F2" s="17" t="s">
+        <v>8</v>
       </c>
-      <c r="G2" s="23" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
+      <c r="G2" s="18" t="s">
+        <v>8</v>
       </c>
-      <c r="H2" s="24" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
+      <c r="H2" s="19" t="s">
+        <v>8</v>
       </c>
     </row>
-    <row r="3" ht="15.75" customFormat="1" customHeight="1" s="13">
-      <c r="A3" s="25" t="inlineStr">
-        <is>
-          <t>Id</t>
-        </is>
+    <row r="3" spans="1:15" s="11" customFormat="1" ht="15.75" customHeight="1">
+      <c r="A3" s="20" t="s">
+        <v>10</v>
       </c>
-      <c r="B3" s="25" t="inlineStr">
-        <is>
-          <t>Title</t>
-        </is>
+      <c r="B3" s="20" t="s">
+        <v>11</v>
       </c>
-      <c r="C3" s="25" t="inlineStr">
-        <is>
-          <t>PartNumber</t>
-        </is>
+      <c r="C3" s="20" t="s">
+        <v>12</v>
       </c>
-      <c r="D3" s="25" t="inlineStr">
-        <is>
-          <t>NarrationTexts</t>
-        </is>
+      <c r="D3" s="20" t="s">
+        <v>13</v>
       </c>
-      <c r="E3" s="25" t="inlineStr">
-        <is>
-          <t>BackgroundImagePath</t>
-        </is>
+      <c r="E3" s="20" t="s">
+        <v>14</v>
       </c>
-      <c r="F3" s="25" t="inlineStr">
-        <is>
-          <t>BackgroundImagePaths</t>
-        </is>
+      <c r="F3" s="20" t="s">
+        <v>15</v>
       </c>
-      <c r="G3" s="25" t="inlineStr">
-        <is>
-          <t>BGMPath</t>
-        </is>
+      <c r="G3" s="20" t="s">
+        <v>16</v>
       </c>
-      <c r="H3" s="26" t="inlineStr">
-        <is>
-          <t>NextGroup</t>
-        </is>
+      <c r="H3" s="21" t="s">
+        <v>17</v>
       </c>
     </row>
-    <row r="4" ht="15.75" customHeight="1">
-      <c r="A4" s="4" t="inlineStr">
-        <is>
-          <t>narration_prologue_01</t>
-        </is>
+    <row r="4" spans="1:15" ht="15.75" customHeight="1">
+      <c r="A4" s="3" t="s">
+        <v>18</v>
       </c>
-      <c r="B4" s="4" t="inlineStr">
-        <is>
-          <t>프롤로그1_줄거리1</t>
-        </is>
+      <c r="B4" s="3" t="s">
+        <v>19</v>
       </c>
-      <c r="C4" s="17" t="n">
+      <c r="C4" s="13">
         <v>1</v>
       </c>
-      <c r="D4" s="19" t="inlineStr">
-        <is>
-          <t>"아득한 옛날, 당시의 조선은 땅 위로 뜨거운 증기가 뿜어져 나오고 거대한 쇠기어들이 맞물려 돌아가는, 세상에서 가장 눈부시고 첨단인 격동의 나라였다네. 이 거대한 영광의 한가운데에는 조선의 스팀펑크 시대를 당당히 열어젖힌 천재 과학자, 장영심이 살고 있었지. 그의 특출난 재주는 당대의 임금인 연산군자의 총애를 한 몸에 받기에 부족함이 없었으나, 하늘은 그에게 천재성을 준 대신 가혹한 외로움도 함께 내렸다네."
-사랑하는 아내를 일찍 여읜 그는 홀로 남은 외딸 장장금을 눈에 넣어도 아프지 않을 귀한 자식으로 정성껏 키워냈다네. 아버지를 닮아 영리했던 장금은 영혼을 울리는 요리 솜씨로 궁중 최고의 요리사가 되어 임금의 귀여움을 독차지했지. 마음씨 곱고 효심 깊은 장금은 매일 밤 붉은 불빛이 새어 나오는 기계실에서, 어머니의 빈자리를 깊고 따뜻한 손맛으로 채우며 홀로 외로이 연구하는 아버지의 유일한 등불이 되어주었다네."</t>
-        </is>
+      <c r="D4" s="14" t="s">
+        <v>46</v>
       </c>
-      <c r="E4" s="5" t="inlineStr">
-        <is>
-          <t>Images/BackGround/Prologue1CutScene1</t>
-        </is>
+      <c r="E4" s="4" t="s">
+        <v>20</v>
       </c>
-      <c r="F4" s="16" t="n"/>
-      <c r="G4" s="5" t="n"/>
-      <c r="H4" s="5" t="n"/>
-      <c r="I4" s="5" t="n"/>
-      <c r="J4" s="5" t="n"/>
-      <c r="K4" s="5" t="n"/>
-      <c r="L4" s="5" t="n"/>
-      <c r="M4" s="5" t="n"/>
-      <c r="N4" s="5" t="n"/>
-      <c r="O4" s="5" t="n"/>
+      <c r="F4" s="12"/>
+      <c r="G4" s="4"/>
+      <c r="H4" s="4"/>
+      <c r="I4" s="4"/>
+      <c r="J4" s="4"/>
+      <c r="K4" s="4"/>
+      <c r="L4" s="4"/>
+      <c r="M4" s="4"/>
+      <c r="N4" s="4"/>
+      <c r="O4" s="4"/>
     </row>
-    <row r="5" ht="15.75" customHeight="1">
-      <c r="A5" s="4" t="inlineStr">
-        <is>
-          <t>narration_prologue_02</t>
-        </is>
+    <row r="5" spans="1:15" ht="15.75" customHeight="1">
+      <c r="A5" s="3" t="s">
+        <v>21</v>
       </c>
-      <c r="B5" s="6" t="inlineStr">
-        <is>
-          <t>프롤로그1_줄거리2</t>
-        </is>
+      <c r="B5" s="5" t="s">
+        <v>22</v>
       </c>
-      <c r="C5" s="6" t="n">
+      <c r="C5" s="5">
         <v>2</v>
       </c>
-      <c r="D5" s="5" t="inlineStr">
-        <is>
-          <t>"그러나 호사다마라 하였던가. 꽃이 온 세상에 흐드러지게 피어날듯 그 눈부신 나이에, 장금에게 홀연히 이름 모를 몹쓸 병이 찾아와 붉은 꽃잎 떨어지듯 허망하게 저물고 말았다네. 장영심은 숨조차 쉬기 힘든 기계의 거친 굉음 속에서, 매일 밤 꺼져가는 불씨처럼 딸의 이름만 부르며 피눈물을 흘렸더랬다. 차디찬 연구실에 홀로 남은 그의 가슴속에는 오직 하나, ‘내 딸을, 그저 단 한 번만이라도 다시 품에 안을 수만 있다면…’ 하는 간절하고도 애달픈 염원만이 시린 새벽달처럼 남아 흐르고 있었다네."</t>
-        </is>
+      <c r="D5" s="4" t="s">
+        <v>23</v>
       </c>
-      <c r="E5" s="5" t="inlineStr">
-        <is>
-          <t>Images/BackGround//Prologue1CutScene2</t>
-        </is>
+      <c r="E5" s="4" t="s">
+        <v>24</v>
       </c>
-      <c r="F5" s="5" t="n"/>
-      <c r="G5" s="5" t="n"/>
-      <c r="H5" s="5" t="n"/>
-      <c r="I5" s="5" t="n"/>
-      <c r="J5" s="5" t="n"/>
-      <c r="K5" s="5" t="n"/>
-      <c r="L5" s="5" t="n"/>
-      <c r="M5" s="5" t="n"/>
-      <c r="N5" s="5" t="n"/>
-      <c r="O5" s="5" t="n"/>
+      <c r="F5" s="4"/>
+      <c r="G5" s="4"/>
+      <c r="H5" s="4"/>
+      <c r="I5" s="4"/>
+      <c r="J5" s="4"/>
+      <c r="K5" s="4"/>
+      <c r="L5" s="4"/>
+      <c r="M5" s="4"/>
+      <c r="N5" s="4"/>
+      <c r="O5" s="4"/>
     </row>
-    <row r="6" ht="15.75" customHeight="1">
-      <c r="A6" s="6" t="inlineStr">
-        <is>
-          <t>narration_prologue_03</t>
-        </is>
+    <row r="6" spans="1:15" ht="15.75" customHeight="1">
+      <c r="A6" s="5" t="s">
+        <v>25</v>
       </c>
-      <c r="B6" s="6" t="inlineStr">
-        <is>
-          <t>프롤로그1_줄거리3</t>
-        </is>
+      <c r="B6" s="5" t="s">
+        <v>26</v>
       </c>
-      <c r="C6" s="6" t="n">
+      <c r="C6" s="5">
         <v>3</v>
       </c>
-      <c r="D6" s="19" t="inlineStr">
-        <is>
-          <t>"그리하여 장영심은 자신의 모든 영혼과 평생을 바친 기술을 쏟아부어, 마치 살아 숨 쉬듯 정교하게 움직이는 목각 인형을 깎아내기 시작했다네. 인형의 얼굴에는 조그만 화면이 신비롭게 박혀 있어, 장금이 생전에 좋아하던 요리와 서툰 감정들을 그림과 글자로 띄울 수 있는 세상에 단 하나뿐인 기적의 발명품이었지."
-매일 밤 째깍거리는 태엽을 감으며, 장영심은 주름진 메마른 두 손을 모아 하늘에 간절히 빌고 또 빌었다네. ‘제발… 이 정교한 나무껍데기에, 내 가여운 아이의 영혼을 잠시만이라도, 단 한 순간만이라도 불어넣어 주소서…’ 하고 말이네."</t>
-        </is>
+      <c r="D6" s="14" t="s">
+        <v>27</v>
       </c>
-      <c r="E6" s="5" t="inlineStr">
-        <is>
-          <t>Images/Background/Prologue1CutScene3</t>
-        </is>
+      <c r="E6" s="4" t="s">
+        <v>28</v>
       </c>
-      <c r="F6" s="5" t="n"/>
-      <c r="G6" s="5" t="n"/>
-      <c r="H6" s="5" t="n"/>
-      <c r="I6" s="5" t="n"/>
-      <c r="J6" s="5" t="n"/>
-      <c r="K6" s="5" t="n"/>
-      <c r="L6" s="5" t="n"/>
-      <c r="M6" s="5" t="n"/>
-      <c r="N6" s="5" t="n"/>
-      <c r="O6" s="5" t="n"/>
+      <c r="F6" s="4"/>
+      <c r="G6" s="4"/>
+      <c r="H6" s="4"/>
+      <c r="I6" s="4"/>
+      <c r="J6" s="4"/>
+      <c r="K6" s="4"/>
+      <c r="L6" s="4"/>
+      <c r="M6" s="4"/>
+      <c r="N6" s="4"/>
+      <c r="O6" s="4"/>
     </row>
-    <row r="7" ht="15.75" customHeight="1">
-      <c r="A7" s="4" t="inlineStr">
-        <is>
-          <t>narration_prologue_04</t>
-        </is>
+    <row r="7" spans="1:15" ht="15.75" customHeight="1">
+      <c r="A7" s="3" t="s">
+        <v>29</v>
       </c>
-      <c r="B7" s="4" t="inlineStr">
-        <is>
-          <t>프롤로그2_줄거리4</t>
-        </is>
+      <c r="B7" s="3" t="s">
+        <v>30</v>
       </c>
-      <c r="C7" s="4" t="n">
+      <c r="C7" s="3">
         <v>4</v>
       </c>
-      <c r="D7" s="5" t="inlineStr">
-        <is>
-          <t>"장영심은 잃어버린 딸 장금이가 생전 가장 아끼던 꽃의 이름을 따, 그 목각 인형에게 ‘모란’이라는 어여쁜 이름을 지어주었다네. 모란은 아버지의 따스한 손길 아래 아장거리는 걸음마부터 다정한 말씨, 그리고 마음을 담아 밥을 짓는 법까지 하나하나 세상을 배워나갔지. 신기하게도 모란은 옛 장금이처럼 요리에 천재적인 재능을 보이며 점차 딸의 모습을 쏙 빼닮아갔어. 비록 투박한 나무 몸뚱이였으나, 두 사람이 붉은 화덕 앞에서 함께 요리하며 웃음 짓던 그 공방은 세상 어느 곳보다 따뜻한 행복으로 가득 차 있었다네."</t>
-        </is>
+      <c r="D7" s="4" t="s">
+        <v>31</v>
       </c>
-      <c r="E7" s="5" t="inlineStr">
-        <is>
-          <t>Images/Background/Prologue2CutScene1</t>
-        </is>
+      <c r="E7" s="4" t="s">
+        <v>32</v>
       </c>
-      <c r="F7" s="5" t="n"/>
-      <c r="G7" s="5" t="n"/>
-      <c r="H7" s="5" t="n"/>
-      <c r="I7" s="5" t="n"/>
-      <c r="J7" s="5" t="n"/>
-      <c r="K7" s="5" t="n"/>
-      <c r="L7" s="5" t="n"/>
-      <c r="M7" s="5" t="n"/>
-      <c r="N7" s="5" t="n"/>
-      <c r="O7" s="5" t="n"/>
+      <c r="F7" s="4"/>
+      <c r="G7" s="4"/>
+      <c r="H7" s="4"/>
+      <c r="I7" s="4"/>
+      <c r="J7" s="4"/>
+      <c r="K7" s="4"/>
+      <c r="L7" s="4"/>
+      <c r="M7" s="4"/>
+      <c r="N7" s="4"/>
+      <c r="O7" s="4"/>
     </row>
-    <row r="8" ht="15.75" customHeight="1">
-      <c r="A8" s="7" t="inlineStr">
-        <is>
-          <t>narration_prologue_05</t>
-        </is>
+    <row r="8" spans="1:15" ht="15.75" customHeight="1">
+      <c r="A8" s="6" t="s">
+        <v>33</v>
       </c>
-      <c r="B8" s="7" t="inlineStr">
-        <is>
-          <t>프롤로그2_줄거리5</t>
-        </is>
+      <c r="B8" s="6" t="s">
+        <v>34</v>
       </c>
-      <c r="C8" s="7" t="n">
+      <c r="C8" s="6">
         <v>5</v>
       </c>
-      <c r="D8" s="19" t="inlineStr">
-        <is>
-          <t>"아침마다 들려오는 모란의 사랑스러운 목소리에 장영심은 시린 가슴을 녹이며 깊은 행복을 느꼈다네. 허나 영원할 것 같았던 그 온기도 무심한 세월 앞에서는 속절없이 스러지고 말았지. 기계 장치들은 녹슬어갔고, 그의 육신 또한 쇠약해져 죽음의 문턱에 다다랐다네. 숨을 거두기 직전, 장영심은 모란의 나뭇결 손을 꼭 쥐고 떨리는 목소리로 마지막 당부를 남겼어.
-“모란아… 이 차가운 기계 몸으로 세상에 태어난 이유를 부디 잊지 말거라. 세상의 그늘진 곳, 도움이 필요한 가여운 자들을 위해 살아가렴. 네가 지어 올린 따뜻한 밥 한 끼가 사람들의 꽁꽁 언 마음을 녹일 수만 있다면… 그것이야말로 네가 세상에 숨 쉬고 있다는 가장 눈부신 증거란다.”
-모란이 눈물 대신 얼굴 화면에 슬픈 파형을 일렁이며 고개를 끄덕이자, 장영심은 남은 힘을 다해 자신의 낡은 갓을 씌워주고 딸 장금이가 입던 요리사복을 품에 안겨준 뒤 조용히 눈을 감았다네. 그렇게 홀로 남은 모란의 주위로 차가운 적막만이 내려앉았지."</t>
-        </is>
+      <c r="D8" s="14" t="s">
+        <v>35</v>
       </c>
-      <c r="E8" s="5" t="inlineStr">
-        <is>
-          <t>Images/Background/Prologue2CutScene2</t>
-        </is>
+      <c r="E8" s="4" t="s">
+        <v>36</v>
       </c>
-      <c r="F8" s="5" t="n"/>
-      <c r="G8" s="5" t="n"/>
-      <c r="H8" s="5" t="n"/>
-      <c r="I8" s="5" t="n"/>
-      <c r="J8" s="5" t="n"/>
-      <c r="K8" s="5" t="n"/>
-      <c r="L8" s="5" t="n"/>
-      <c r="M8" s="5" t="n"/>
-      <c r="N8" s="5" t="n"/>
-      <c r="O8" s="5" t="n"/>
+      <c r="F8" s="4"/>
+      <c r="G8" s="4"/>
+      <c r="H8" s="4"/>
+      <c r="I8" s="4"/>
+      <c r="J8" s="4"/>
+      <c r="K8" s="4"/>
+      <c r="L8" s="4"/>
+      <c r="M8" s="4"/>
+      <c r="N8" s="4"/>
+      <c r="O8" s="4"/>
     </row>
-    <row r="9" ht="15.75" customHeight="1">
-      <c r="A9" s="7" t="inlineStr">
-        <is>
-          <t>narration_prologue_06</t>
-        </is>
+    <row r="9" spans="1:15" ht="15.75" customHeight="1">
+      <c r="A9" s="6" t="s">
+        <v>37</v>
       </c>
-      <c r="B9" s="7" t="inlineStr">
-        <is>
-          <t>프롤로그2_줄거리6</t>
-        </is>
+      <c r="B9" s="6" t="s">
+        <v>38</v>
       </c>
-      <c r="C9" s="7" t="n">
+      <c r="C9" s="6">
         <v>6</v>
       </c>
-      <c r="D9" s="19" t="inlineStr">
-        <is>
-          <t xml:space="preserve">"그 무렵, 찬란했던 조선은 칠흑 같은 어둠 속으로 속절없이 가라앉고 있었다네. 조선의 놀라운 기술을 탐낸 외세의 위협이 끊이지 않자, 임금 연산군은 극심한 번뇌 속에서 마음에 깊은 병을 얻고 말았지. 설상가상으로 입맛을 달래주던 으뜸 요리사 장금과 기적을 빚어내던 천재 과학자 장영심마저 연이어 세상을 떠나버리니, 임금의 광기를 잠재울 방도도 조선의 톱니바퀴도 모두 멈춰버린 게야.
-이성을 잃고 괴팍해진 임금은 분노와 우울에 휩싸여 탐관오리들을 풀었고, 백성들의 삶은 가혹하게 짓밟히고 말았다네. 온 나라에 굶주림과 곡소리가 하늘을 찌르던 바로 그 비통한 때…… 굶주린 백성을 구하고 병든 조선의 마음을 치유하기 위한, 모란의 위대한 여정이 마침내 첫발을 내딛게 된 것이라네."
-</t>
-        </is>
+      <c r="D9" s="14" t="s">
+        <v>47</v>
       </c>
-      <c r="E9" s="5" t="inlineStr">
-        <is>
-          <t>Images/Background/Prologue2CutScene3</t>
-        </is>
+      <c r="E9" s="4" t="s">
+        <v>45</v>
       </c>
-      <c r="F9" s="5" t="n"/>
-      <c r="G9" s="5" t="n"/>
-      <c r="H9" s="5" t="n"/>
-      <c r="I9" s="5" t="n"/>
-      <c r="J9" s="5" t="n"/>
-      <c r="K9" s="5" t="n"/>
-      <c r="L9" s="5" t="n"/>
-      <c r="M9" s="5" t="n"/>
-      <c r="N9" s="5" t="n"/>
-      <c r="O9" s="5" t="n"/>
+      <c r="F9" s="4"/>
+      <c r="G9" s="4"/>
+      <c r="H9" s="4"/>
+      <c r="I9" s="4"/>
+      <c r="J9" s="4"/>
+      <c r="K9" s="4"/>
+      <c r="L9" s="4"/>
+      <c r="M9" s="4"/>
+      <c r="N9" s="4"/>
+      <c r="O9" s="4"/>
     </row>
-    <row r="10" ht="15.75" customHeight="1">
-      <c r="A10" s="1" t="inlineStr">
-        <is>
-          <t>narration_prologue_07</t>
-        </is>
+    <row r="10" spans="1:15" ht="15.75" customHeight="1">
+      <c r="A10" s="1" t="s">
+        <v>40</v>
       </c>
-      <c r="B10" s="1" t="inlineStr">
-        <is>
-          <t>시나리오1_줄거리1</t>
-        </is>
+      <c r="B10" s="1" t="s">
+        <v>41</v>
       </c>
-      <c r="C10" s="1" t="n">
+      <c r="C10" s="1">
         <v>7</v>
       </c>
-      <c r="D10" s="19" t="inlineStr">
-        <is>
-          <t xml:space="preserve">“모란이 지어내는 요리는 결코 평범한 음식이 아니었다네. 장장금의 따뜻한 영혼이 한데 어우러져 빚어낸, 세상에 단 하나뿐인 영묘한 기적의 음식이었지.
-먹는 이의 가장 깊고 간절한 갈망을 헤아려, 그 소원을 풀어주고, 차갑게 얼어붙은 마음을 선한 쪽으로 되돌려주는 마법 같은 치유의 힘이 깃들어 있었다네.
-그 날 배고픔에 지친 작은 강아지 하나가 모란의 집에 스며들어 이 장영심의 제삿상을 허겁지겁 먹어 치우니, 재익의 몸 속에서 뜨거운 기운이 용솟음치며, 털이 곤두서고, 몸이 부풀며, 네 다리가 두 다리로 변하는 기이한 변화가 일어났다네.
-그의 오랜 세월 마음속 깊이 간직했던, ‘사람이 되어 춘양 아씨를 모시고 싶다’라는 그 간절한 소원이 모란의 음식으로 인해 마침내 이루어진 것이었네.”
-</t>
-        </is>
+      <c r="D10" s="14" t="s">
+        <v>42</v>
       </c>
-      <c r="E10" s="5" t="n"/>
-      <c r="F10" s="5" t="n"/>
-      <c r="G10" s="5" t="n"/>
-      <c r="H10" s="5" t="n"/>
-      <c r="I10" s="5" t="n"/>
-      <c r="J10" s="5" t="n"/>
-      <c r="K10" s="5" t="n"/>
-      <c r="L10" s="5" t="n"/>
-      <c r="M10" s="5" t="n"/>
-      <c r="N10" s="5" t="n"/>
-      <c r="O10" s="5" t="n"/>
+      <c r="E10" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="F10" s="4"/>
+      <c r="G10" s="4"/>
+      <c r="H10" s="4"/>
+      <c r="I10" s="4"/>
+      <c r="J10" s="4"/>
+      <c r="K10" s="4"/>
+      <c r="L10" s="4"/>
+      <c r="M10" s="4"/>
+      <c r="N10" s="4"/>
+      <c r="O10" s="4"/>
     </row>
-    <row r="11" ht="15.75" customHeight="1">
-      <c r="A11" s="1" t="n"/>
-      <c r="B11" s="1" t="n"/>
-      <c r="C11" s="1" t="n"/>
-      <c r="D11" s="5" t="n"/>
-      <c r="E11" s="5" t="n"/>
-      <c r="F11" s="5" t="n"/>
-      <c r="G11" s="5" t="n"/>
-      <c r="H11" s="5" t="n"/>
-      <c r="I11" s="5" t="n"/>
-      <c r="J11" s="5" t="n"/>
-      <c r="K11" s="5" t="n"/>
-      <c r="L11" s="5" t="n"/>
-      <c r="M11" s="5" t="n"/>
-      <c r="N11" s="5" t="n"/>
-      <c r="O11" s="5" t="n"/>
+    <row r="11" spans="1:15" ht="15.75" customHeight="1">
+      <c r="A11" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="B11" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="C11" s="1">
+        <v>8</v>
+      </c>
+      <c r="D11" s="14" t="s">
+        <v>48</v>
+      </c>
+      <c r="E11" s="4" t="s">
+        <v>51</v>
+      </c>
+      <c r="F11" s="4"/>
+      <c r="G11" s="4"/>
+      <c r="H11" s="4"/>
+      <c r="I11" s="4"/>
+      <c r="J11" s="4"/>
+      <c r="K11" s="4"/>
+      <c r="L11" s="4"/>
+      <c r="M11" s="4"/>
+      <c r="N11" s="4"/>
+      <c r="O11" s="4"/>
     </row>
-    <row r="12" ht="15.75" customHeight="1">
-      <c r="A12" s="7" t="n"/>
-      <c r="B12" s="7" t="n"/>
-      <c r="C12" s="7" t="n"/>
-      <c r="D12" s="5" t="n"/>
-      <c r="E12" s="5" t="n"/>
-      <c r="F12" s="5" t="n"/>
-      <c r="G12" s="5" t="n"/>
-      <c r="H12" s="5" t="n"/>
-      <c r="I12" s="5" t="n"/>
-      <c r="J12" s="5" t="n"/>
-      <c r="K12" s="5" t="n"/>
-      <c r="L12" s="5" t="n"/>
-      <c r="M12" s="5" t="n"/>
-      <c r="N12" s="5" t="n"/>
-      <c r="O12" s="5" t="n"/>
+    <row r="12" spans="1:15" ht="15.75" customHeight="1">
+      <c r="A12" s="6" t="s">
+        <v>49</v>
+      </c>
+      <c r="B12" s="6" t="s">
+        <v>50</v>
+      </c>
+      <c r="C12" s="6">
+        <v>9</v>
+      </c>
+      <c r="D12" s="14" t="s">
+        <v>52</v>
+      </c>
+      <c r="E12" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="F12" s="4"/>
+      <c r="G12" s="4"/>
+      <c r="H12" s="4"/>
+      <c r="I12" s="4"/>
+      <c r="J12" s="4"/>
+      <c r="K12" s="4"/>
+      <c r="L12" s="4"/>
+      <c r="M12" s="4"/>
+      <c r="N12" s="4"/>
+      <c r="O12" s="4"/>
     </row>
-    <row r="13" ht="15.75" customHeight="1">
-      <c r="A13" s="4" t="n"/>
-      <c r="B13" s="4" t="n"/>
-      <c r="C13" s="4" t="n"/>
-      <c r="D13" s="5" t="n"/>
-      <c r="E13" s="5" t="n"/>
-      <c r="F13" s="5" t="n"/>
-      <c r="G13" s="5" t="n"/>
-      <c r="H13" s="5" t="n"/>
-      <c r="I13" s="5" t="n"/>
-      <c r="J13" s="5" t="n"/>
-      <c r="K13" s="5" t="n"/>
-      <c r="L13" s="5" t="n"/>
-      <c r="M13" s="5" t="n"/>
-      <c r="N13" s="5" t="n"/>
-      <c r="O13" s="5" t="n"/>
+    <row r="13" spans="1:15" ht="15.75" customHeight="1">
+      <c r="A13" s="3"/>
+      <c r="B13" s="3"/>
+      <c r="C13" s="3"/>
+      <c r="D13" s="4"/>
+      <c r="E13" s="4"/>
+      <c r="F13" s="4"/>
+      <c r="G13" s="4"/>
+      <c r="H13" s="4"/>
+      <c r="I13" s="4"/>
+      <c r="J13" s="4"/>
+      <c r="K13" s="4"/>
+      <c r="L13" s="4"/>
+      <c r="M13" s="4"/>
+      <c r="N13" s="4"/>
+      <c r="O13" s="4"/>
     </row>
-    <row r="14" ht="15.75" customHeight="1">
-      <c r="A14" s="1" t="n"/>
-      <c r="B14" s="1" t="n"/>
-      <c r="C14" s="1" t="n"/>
-      <c r="D14" s="5" t="n"/>
-      <c r="E14" s="5" t="n"/>
-      <c r="F14" s="5" t="n"/>
-      <c r="G14" s="5" t="n"/>
-      <c r="H14" s="5" t="n"/>
-      <c r="I14" s="5" t="n"/>
-      <c r="J14" s="5" t="n"/>
-      <c r="K14" s="5" t="n"/>
-      <c r="L14" s="5" t="n"/>
-      <c r="M14" s="5" t="n"/>
-      <c r="N14" s="5" t="n"/>
-      <c r="O14" s="5" t="n"/>
+    <row r="14" spans="1:15" ht="15.75" customHeight="1">
+      <c r="A14" s="1"/>
+      <c r="B14" s="1"/>
+      <c r="C14" s="1"/>
+      <c r="D14" s="4"/>
+      <c r="E14" s="4"/>
+      <c r="F14" s="4"/>
+      <c r="G14" s="4"/>
+      <c r="H14" s="4"/>
+      <c r="I14" s="4"/>
+      <c r="J14" s="4"/>
+      <c r="K14" s="4"/>
+      <c r="L14" s="4"/>
+      <c r="M14" s="4"/>
+      <c r="N14" s="4"/>
+      <c r="O14" s="4"/>
     </row>
-    <row r="15" ht="15.75" customHeight="1">
-      <c r="A15" s="1" t="n"/>
-      <c r="B15" s="1" t="n"/>
-      <c r="C15" s="1" t="n"/>
-      <c r="D15" s="5" t="n"/>
-      <c r="E15" s="5" t="n"/>
-      <c r="F15" s="5" t="n"/>
-      <c r="G15" s="5" t="n"/>
-      <c r="H15" s="5" t="n"/>
-      <c r="I15" s="5" t="n"/>
-      <c r="J15" s="5" t="n"/>
-      <c r="K15" s="5" t="n"/>
-      <c r="L15" s="5" t="n"/>
-      <c r="M15" s="5" t="n"/>
-      <c r="N15" s="5" t="n"/>
-      <c r="O15" s="5" t="n"/>
+    <row r="15" spans="1:15" ht="15.75" customHeight="1">
+      <c r="A15" s="1"/>
+      <c r="B15" s="1"/>
+      <c r="C15" s="1"/>
+      <c r="D15" s="4"/>
+      <c r="E15" s="4"/>
+      <c r="F15" s="4"/>
+      <c r="G15" s="4"/>
+      <c r="H15" s="4"/>
+      <c r="I15" s="4"/>
+      <c r="J15" s="4"/>
+      <c r="K15" s="4"/>
+      <c r="L15" s="4"/>
+      <c r="M15" s="4"/>
+      <c r="N15" s="4"/>
+      <c r="O15" s="4"/>
     </row>
-    <row r="16" ht="15.75" customHeight="1">
-      <c r="A16" s="8" t="n"/>
-      <c r="B16" s="8" t="n"/>
-      <c r="C16" s="8" t="n"/>
+    <row r="16" spans="1:15" ht="15.75" customHeight="1">
+      <c r="A16" s="7"/>
+      <c r="B16" s="7"/>
+      <c r="C16" s="7"/>
     </row>
-    <row r="17" ht="15.75" customHeight="1">
-      <c r="A17" s="9" t="n"/>
-      <c r="B17" s="9" t="n"/>
-      <c r="C17" s="9" t="n"/>
+    <row r="17" spans="1:5" ht="15.75" customHeight="1">
+      <c r="A17" s="8"/>
+      <c r="B17" s="8"/>
+      <c r="C17" s="8"/>
     </row>
-    <row r="18" ht="15.75" customHeight="1">
-      <c r="A18" s="9" t="n"/>
-      <c r="B18" s="9" t="n"/>
-      <c r="C18" s="9" t="n"/>
+    <row r="18" spans="1:5" ht="15.75" customHeight="1">
+      <c r="A18" s="8"/>
+      <c r="B18" s="8"/>
+      <c r="C18" s="8"/>
     </row>
-    <row r="19" ht="15.75" customHeight="1">
-      <c r="A19" s="9" t="n"/>
-      <c r="B19" s="9" t="n"/>
-      <c r="C19" s="9" t="n"/>
-      <c r="D19" s="5" t="n"/>
-      <c r="E19" s="5" t="n"/>
+    <row r="19" spans="1:5" ht="15.75" customHeight="1">
+      <c r="A19" s="8"/>
+      <c r="B19" s="8"/>
+      <c r="C19" s="8"/>
+      <c r="D19" s="4"/>
+      <c r="E19" s="4"/>
     </row>
-    <row r="20" ht="15.75" customHeight="1">
-      <c r="A20" s="9" t="n"/>
-      <c r="B20" s="9" t="n"/>
-      <c r="C20" s="9" t="n"/>
+    <row r="20" spans="1:5" ht="15.75" customHeight="1">
+      <c r="A20" s="8"/>
+      <c r="B20" s="8"/>
+      <c r="C20" s="8"/>
     </row>
-    <row r="21" ht="15.75" customHeight="1">
-      <c r="A21" s="9" t="n"/>
-      <c r="B21" s="9" t="n"/>
-      <c r="C21" s="9" t="n"/>
+    <row r="21" spans="1:5" ht="15.75" customHeight="1">
+      <c r="A21" s="8"/>
+      <c r="B21" s="8"/>
+      <c r="C21" s="8"/>
     </row>
-    <row r="22" ht="15.75" customHeight="1">
-      <c r="A22" s="9" t="n"/>
-      <c r="B22" s="9" t="n"/>
-      <c r="C22" s="9" t="n"/>
+    <row r="22" spans="1:5" ht="15.75" customHeight="1">
+      <c r="A22" s="8"/>
+      <c r="B22" s="8"/>
+      <c r="C22" s="8"/>
     </row>
-    <row r="23" ht="15.75" customHeight="1">
-      <c r="A23" s="9" t="n"/>
-      <c r="B23" s="9" t="n"/>
-      <c r="C23" s="9" t="n"/>
+    <row r="23" spans="1:5" ht="15.75" customHeight="1">
+      <c r="A23" s="8"/>
+      <c r="B23" s="8"/>
+      <c r="C23" s="8"/>
     </row>
-    <row r="24" ht="15.75" customHeight="1">
-      <c r="A24" s="9" t="n"/>
-      <c r="B24" s="9" t="n"/>
-      <c r="C24" s="9" t="n"/>
+    <row r="24" spans="1:5" ht="15.75" customHeight="1">
+      <c r="A24" s="8"/>
+      <c r="B24" s="8"/>
+      <c r="C24" s="8"/>
     </row>
-    <row r="25" ht="15.75" customHeight="1">
-      <c r="A25" s="9" t="n"/>
-      <c r="B25" s="9" t="n"/>
-      <c r="C25" s="9" t="n"/>
-      <c r="E25" s="5" t="n"/>
+    <row r="25" spans="1:5" ht="15.75" customHeight="1">
+      <c r="A25" s="8"/>
+      <c r="B25" s="8"/>
+      <c r="C25" s="8"/>
+      <c r="E25" s="4"/>
     </row>
-    <row r="26" ht="15.75" customHeight="1">
-      <c r="A26" s="10" t="n"/>
-      <c r="B26" s="10" t="n"/>
-      <c r="C26" s="10" t="n"/>
-      <c r="E26" s="5" t="n"/>
+    <row r="26" spans="1:5" ht="15.75" customHeight="1">
+      <c r="A26" s="9"/>
+      <c r="B26" s="9"/>
+      <c r="C26" s="9"/>
+      <c r="E26" s="4"/>
     </row>
-    <row r="27" ht="15.75" customHeight="1">
-      <c r="A27" s="10" t="n"/>
-      <c r="B27" s="10" t="n"/>
-      <c r="C27" s="10" t="n"/>
-      <c r="E27" s="5" t="n"/>
+    <row r="27" spans="1:5" ht="15.75" customHeight="1">
+      <c r="A27" s="9"/>
+      <c r="B27" s="9"/>
+      <c r="C27" s="9"/>
+      <c r="E27" s="4"/>
     </row>
-    <row r="28" ht="15.75" customHeight="1">
-      <c r="A28" s="10" t="n"/>
-      <c r="B28" s="10" t="n"/>
-      <c r="C28" s="10" t="n"/>
-      <c r="E28" s="5" t="n"/>
+    <row r="28" spans="1:5" ht="15.75" customHeight="1">
+      <c r="A28" s="9"/>
+      <c r="B28" s="9"/>
+      <c r="C28" s="9"/>
+      <c r="E28" s="4"/>
     </row>
-    <row r="29" ht="15.75" customHeight="1">
-      <c r="A29" s="10" t="n"/>
-      <c r="B29" s="10" t="n"/>
-      <c r="C29" s="10" t="n"/>
+    <row r="29" spans="1:5" ht="15.75" customHeight="1">
+      <c r="A29" s="9"/>
+      <c r="B29" s="9"/>
+      <c r="C29" s="9"/>
     </row>
-    <row r="30" ht="15.75" customHeight="1">
-      <c r="A30" s="10" t="n"/>
-      <c r="B30" s="10" t="n"/>
-      <c r="C30" s="10" t="n"/>
+    <row r="30" spans="1:5" ht="15.75" customHeight="1">
+      <c r="A30" s="9"/>
+      <c r="B30" s="9"/>
+      <c r="C30" s="9"/>
     </row>
-    <row r="31" ht="15.75" customHeight="1">
-      <c r="A31" s="10" t="n"/>
-      <c r="B31" s="10" t="n"/>
-      <c r="C31" s="10" t="n"/>
+    <row r="31" spans="1:5" ht="15.75" customHeight="1">
+      <c r="A31" s="9"/>
+      <c r="B31" s="9"/>
+      <c r="C31" s="9"/>
     </row>
-    <row r="32" ht="15.75" customHeight="1">
-      <c r="A32" s="11" t="n"/>
-      <c r="B32" s="11" t="n"/>
-      <c r="C32" s="11" t="n"/>
+    <row r="32" spans="1:5" ht="15.75" customHeight="1">
+      <c r="A32" s="10"/>
+      <c r="B32" s="10"/>
+      <c r="C32" s="10"/>
     </row>
-    <row r="33" ht="15.75" customHeight="1">
-      <c r="A33" s="11" t="n"/>
-      <c r="B33" s="11" t="n"/>
-      <c r="C33" s="11" t="n"/>
+    <row r="33" spans="1:3" ht="15.75" customHeight="1">
+      <c r="A33" s="10"/>
+      <c r="B33" s="10"/>
+      <c r="C33" s="10"/>
     </row>
-    <row r="34" ht="15.75" customHeight="1">
-      <c r="A34" s="11" t="n"/>
-      <c r="B34" s="11" t="n"/>
-      <c r="C34" s="11" t="n"/>
+    <row r="34" spans="1:3" ht="15.75" customHeight="1">
+      <c r="A34" s="10"/>
+      <c r="B34" s="10"/>
+      <c r="C34" s="10"/>
     </row>
-    <row r="35" ht="15.75" customHeight="1">
-      <c r="A35" s="11" t="n"/>
-      <c r="B35" s="11" t="n"/>
-      <c r="C35" s="11" t="n"/>
+    <row r="35" spans="1:3" ht="15.75" customHeight="1">
+      <c r="A35" s="10"/>
+      <c r="B35" s="10"/>
+      <c r="C35" s="10"/>
     </row>
-    <row r="36" ht="15.75" customHeight="1"/>
-    <row r="37" ht="15.75" customHeight="1"/>
-    <row r="38" ht="15.75" customHeight="1"/>
-    <row r="39" ht="15.75" customHeight="1"/>
-    <row r="40" ht="15.75" customHeight="1"/>
-    <row r="41" ht="15.75" customHeight="1"/>
-    <row r="42" ht="15.75" customHeight="1"/>
-    <row r="43" ht="15.75" customHeight="1"/>
-    <row r="44" ht="15.75" customHeight="1"/>
-    <row r="45" ht="15.75" customHeight="1"/>
-    <row r="46" ht="15.75" customHeight="1"/>
-    <row r="47" ht="15.75" customHeight="1"/>
-    <row r="48" ht="15.75" customHeight="1"/>
+    <row r="36" spans="1:3" ht="15.75" customHeight="1"/>
+    <row r="37" spans="1:3" ht="15.75" customHeight="1"/>
+    <row r="38" spans="1:3" ht="15.75" customHeight="1"/>
+    <row r="39" spans="1:3" ht="15.75" customHeight="1"/>
+    <row r="40" spans="1:3" ht="15.75" customHeight="1"/>
+    <row r="41" spans="1:3" ht="15.75" customHeight="1"/>
+    <row r="42" spans="1:3" ht="15.75" customHeight="1"/>
+    <row r="43" spans="1:3" ht="15.75" customHeight="1"/>
+    <row r="44" spans="1:3" ht="15.75" customHeight="1"/>
+    <row r="45" spans="1:3" ht="15.75" customHeight="1"/>
+    <row r="46" spans="1:3" ht="15.75" customHeight="1"/>
+    <row r="47" spans="1:3" ht="15.75" customHeight="1"/>
+    <row r="48" spans="1:3" ht="15.75" customHeight="1"/>
     <row r="49" ht="15.75" customHeight="1"/>
     <row r="50" ht="15.75" customHeight="1"/>
     <row r="51" ht="15.75" customHeight="1"/>
@@ -2073,7 +9977,8 @@
     <row r="999" ht="15.75" customHeight="1"/>
     <row r="1000" ht="15.75" customHeight="1"/>
   </sheetData>
+  <phoneticPr fontId="4" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" paperSize="9"/>
+  <pageSetup paperSize="9" orientation="portrait"/>
 </worksheet>
 </file>
--- a/JsonConverter/ExcelFiles/OO_Narration.xlsx
+++ b/JsonConverter/ExcelFiles/OO_Narration.xlsx
@@ -152,10 +152,6 @@
 </t>
   </si>
   <si>
-    <t>narration_prologue_08</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
     <t>프리파이널_줄거리8</t>
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
@@ -8100,6 +8096,10 @@
       </rPr>
       <t/>
     </r>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>narration_prologue_08</t>
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
 </sst>
@@ -8622,7 +8622,7 @@
         <v>1</v>
       </c>
       <c r="D4" s="14" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="E4" s="4" t="s">
         <v>20</v>
@@ -8757,10 +8757,10 @@
         <v>6</v>
       </c>
       <c r="D9" s="14" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="E9" s="4" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="F9" s="4"/>
       <c r="G9" s="4"/>
@@ -8802,19 +8802,19 @@
     </row>
     <row r="11" spans="1:15" ht="15.75" customHeight="1">
       <c r="A11" s="1" t="s">
-        <v>43</v>
+        <v>52</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C11" s="1">
         <v>8</v>
       </c>
       <c r="D11" s="14" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="E11" s="4" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="F11" s="4"/>
       <c r="G11" s="4"/>
@@ -8829,19 +8829,19 @@
     </row>
     <row r="12" spans="1:15" ht="15.75" customHeight="1">
       <c r="A12" s="6" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B12" s="6" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C12" s="6">
         <v>9</v>
       </c>
       <c r="D12" s="14" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="E12" s="4" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="F12" s="4"/>
       <c r="G12" s="4"/>
@@ -9979,6 +9979,6 @@
   </sheetData>
   <phoneticPr fontId="4" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>